--- a/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/Instrumentos de evaluación/TC1/05_TC1_Rubrica.xlsx
+++ b/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/Instrumentos de evaluación/TC1/05_TC1_Rubrica.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -104,11 +104,55 @@
         <color rgb="009E9E9E"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -149,6 +193,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,6 +577,11 @@
           <t>RÚBRICA DE EVALUACIÓN DE LA PRESENTACIÓN</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="15" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -553,6 +604,8 @@
           <t>Controles de impactos ambientales</t>
         </is>
       </c>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -575,6 +628,8 @@
           <t>Informe de descripción de la matriz + anexo + PPT</t>
         </is>
       </c>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -582,6 +637,11 @@
           <t>La suma de los cinco criterios ES la nota vigesimal: 5 criterios × 4 puntos = 20.</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
@@ -589,6 +649,9 @@
           <t>Excelente          ·          Bueno          ·          Regular          ·          En inicio</t>
         </is>
       </c>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -622,7 +685,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="74" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Comprensión del problema</t>
@@ -630,27 +693,165 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Describe qué registra la matriz del taller y para qué sirve; ubica las diecisiete actividades y describe entrada y salida de las que la matriz recoge, señalando cuál de las actividades del relato no tiene fila.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Ubica las diecisiete actividades del taller con su entrada y su salida, dice qué registra cada columna de la matriz </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y señala la actividad que no tiene fila.</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Describe qué registra la matriz y ubica las actividades con su entrada y su salida, pero no llega a señalar la actividad que falta.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Ubica </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">las diecisiete </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">actividades del taller con su entrada y su salida, y dice qué registra </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cada columna de </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>la matriz.</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Describe la matriz por encima: enumera columnas sin decir qué registra cada una, o confunde la entrada con la salida en más de una actividad.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Ubica doce </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">o más </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">actividades del taller con </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">su entrada y su </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">salida, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y dice qué registra la matriz por encima.</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Describe el caso sin decir qué registra la matriz; repite el relato del taller.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Ubica </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">menos de </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">doce actividades del taller y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">confunde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>entrada con la salida en alguna.</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="9" t="n"/>
     </row>
-    <row r="9" ht="74" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Desarrollo técnico</t>
@@ -658,106 +859,673 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Relaciona cada actividad con su aspecto y su impacto sin confundirlos, y describe fila por fila cómo el procedimiento obtiene el nivel de impacto —severidad por probabilidad— y en qué tramo de la tabla cae la clasificación.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Relaciona cada actividad con su aspecto y su impacto sin confundir uno con otro, describe cómo el procedimiento obtiene el nivel de impacto </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y acierta el tramo de la clasificación.</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Relaciona aspecto e impacto correctamente y describe cómo se obtiene el nivel, pero se equivoca en el tramo de la tabla en alguna fila.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Relaciona </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cada actividad </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con su aspecto y su impacto </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">sin confundir uno con otro, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">y describe </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cómo el procedimiento obtiene </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>el nivel de impacto.</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Confunde el aspecto con el impacto en alguna actividad, o describe el nivel de impacto sin decir de dónde salen los dos criterios que lo componen.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Relaciona </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la mayoría de las </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">actividades con su aspecto y su impacto, y describe el nivel de impacto </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sin decir de dónde sale.</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Menciona aspectos e impactos sueltos sin relacionarlos con la actividad que los genera, y no describe cómo se obtiene el nivel de impacto.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Relaciona </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">pocas </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">actividades con su aspecto y su impacto, y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">no </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">describe </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cómo se obtiene </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>el nivel de impacto.</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
     </row>
-    <row r="10" ht="74" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Conclusiones y análisis de resultados</t>
+          <t>Conclusiones</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Describe qué aspectos quedan significativos y por qué regla, señalando que la clasificación de una fila no corresponde a lo que el procedimiento manda cuando hay requisito legal; describe el control que a ese aspecto le toca.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué aspectos quedan significativos y con qué regla, señala la fila que el requisito legal hace significativa, describe el control que le toca </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y dice qué aspecto queda sin gestionar.</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Describe qué aspectos quedan significativos y señala la fila mal clasificada, pero no describe qué control le corresponde.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué aspectos quedan significativos y con qué regla, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">señala </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la fila que el requisito legal hace significativa </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y describe el control que le toca.</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Describe la clasificación tal como la matriz la trae, sin contrastarla con lo que el procedimiento manda.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué aspectos quedan significativos </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con qué regla, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">y pasa por alto la fila </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>el requisito legal hace significativa.</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Las conclusiones no distinguen los aspectos significativos de los que no lo son, o no se apoyan en el procedimiento.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué aspectos quedan significativos </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">copiando la matriz, sin decir </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con qué regla </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">ni </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">qué </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>control les toca.</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="9" t="n"/>
     </row>
-    <row r="11" ht="74" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Presentación PPT: contenido y diseño</t>
+          <t>Organización y presentación del producto</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>El PPT recorre las cinco láminas sin saltarse ninguna sección del informe; la matriz se muestra legible y lo señalado se distingue a simple vista.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y lleva su contenido en cuadro o esquema, con su sustento a la vista, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y se entiende sin que el expositor la explique.</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Recorre las cinco láminas pero una queda apretada o ilegible.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y lleva su contenido en </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cuadro o esquema, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>con su sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Faltan dos o más láminas de contenido, o la matriz se proyecta ilegible.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">lleva su contenido en texto corrido, con su </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>El PPT reproduce la matriz copiada sin señalar nada, o no cubre el informe.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">vuelca sus párrafos, sin el </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
-    <row r="12" ht="74" customHeight="1">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Presentación oral: dominio y claridad</t>
+          <t>Sustentación oral</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Los cuatro integrantes exponen la parte que les tocó y responden la pregunta del instructor sobre una parte que no expusieron.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Todos los integrantes exponen la parte que les corresponde con orden y claridad, dentro del tiempo asignado, y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cualquiera </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">responde consultas </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sobre una parte que no expuso.</t>
+          </r>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Los cuatro exponen su rol y el equipo responde, pero alguno no domina la parte ajena.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Todos los </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">integrantes exponen la parte que les corresponde con orden y claridad, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">dentro </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">las </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>consultas del instructor.</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Algunos integrantes exponen con ideas sueltas o leyendo la lámina.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Algunos integrantes exponen </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la parte que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">les </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">corresponde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con orden y claridad, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">se </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">pasan </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">algunas </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>consultas del instructor.</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Solo un integrante expone; el equipo no responde por las partes ajenas.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Un integrante expone </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la parte que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">le </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">corresponde, se </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">pasa </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">las </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">consultas del instructor </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>con imprecisión.</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -779,6 +1547,11 @@
           <t>NOTAS ESPECÍFICAS   ·   Excelente (4): está completo y correcto.   Bueno (3): completo con un fallo menor.   Regular (2): falta una pieza o hay confusión de fondo.   En inicio (1): no cumple lo que el criterio pide.</t>
         </is>
       </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -821,7 +1594,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3 · Conclusiones y análisis de resultados</t>
+          <t>3 · Conclusiones</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -833,7 +1606,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>4 · Presentación PPT: contenido y diseño</t>
+          <t>4 · Organización y presentación del producto</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -845,7 +1618,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>5 · Presentación oral: dominio y claridad</t>
+          <t>5 · Sustentación oral</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
